--- a/apps/super-admin/public/templates/question-import-template.xlsx
+++ b/apps/super-admin/public/templates/question-import-template.xlsx
@@ -2,7 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Bank_Soal_Tryout" sheetId="1" r:id="R3878c938efe54934"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Bank Soal" sheetId="1" r:id="R0004293953504ff4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Petunjuk" sheetId="2" r:id="Re4b8eb3549f9444a"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -13,25 +14,19 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:fonts count="3">
+  <x:fonts count="2">
     <x:font>
       <x:sz val="11"/>
       <x:name val="Carlito"/>
     </x:font>
     <x:font>
       <x:b/>
-      <x:sz val="14"/>
+      <x:sz val="11"/>
       <x:color rgb="FFFFFFFF"/>
       <x:name val="Carlito"/>
     </x:font>
-    <x:font>
-      <x:b/>
-      <x:sz val="11"/>
-      <x:color rgb="FF17312D"/>
-      <x:name val="Carlito"/>
-    </x:font>
   </x:fonts>
-  <x:fills count="4">
+  <x:fills count="3">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -40,12 +35,7 @@
     </x:fill>
     <x:fill>
       <x:patternFill patternType="solid">
-        <x:fgColor rgb="FF0A7C6E"/>
-      </x:patternFill>
-    </x:fill>
-    <x:fill>
-      <x:patternFill patternType="solid">
-        <x:fgColor rgb="FFF59E0B"/>
+        <x:fgColor rgb="FF0F766E"/>
       </x:patternFill>
     </x:fill>
   </x:fills>
@@ -56,25 +46,42 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="13">
+  <x:cellXfs count="16">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment wrapText="1"/>
+    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
@@ -233,137 +240,394 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="22" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="22" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="22" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="22" hidden="0" customWidth="1"/>
-    <x:col min="5" max="5" width="22" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="18" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="20" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="24" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="10" hidden="0" customWidth="1"/>
     <x:col min="6" max="6" width="22" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="32" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="32" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="32" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="32" hidden="0" customWidth="1"/>
-    <x:col min="11" max="11" width="32" hidden="0" customWidth="1"/>
-    <x:col min="12" max="12" width="32" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="18" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="18" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="14" hidden="0" customWidth="1"/>
+    <x:col min="10" max="10" width="14" hidden="0" customWidth="1"/>
+    <x:col min="11" max="11" width="28" hidden="0" customWidth="1"/>
+    <x:col min="12" max="12" width="38" hidden="0" customWidth="1"/>
     <x:col min="13" max="13" width="32" hidden="0" customWidth="1"/>
     <x:col min="14" max="14" width="32" hidden="0" customWidth="1"/>
     <x:col min="15" max="15" width="32" hidden="0" customWidth="1"/>
+    <x:col min="16" max="16" width="32" hidden="0" customWidth="1"/>
+    <x:col min="17" max="17" width="24" hidden="0" customWidth="1"/>
+    <x:col min="18" max="18" width="18" hidden="0" customWidth="1"/>
+    <x:col min="19" max="19" width="42" hidden="0" customWidth="1"/>
+    <x:col min="20" max="20" width="42" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1" ht="28" customHeight="1">
-      <x:c r="A1" s="4" t="str">
-        <x:v>Template Bank Soal Berdasarkan Tryout</x:v>
-      </x:c>
-      <x:c r="B1" s="4" t="str"/>
-      <x:c r="C1" s="4" t="str"/>
-      <x:c r="D1" s="4" t="str"/>
-      <x:c r="E1" s="4" t="str"/>
-      <x:c r="F1" s="4" t="str"/>
-      <x:c r="G1" s="4" t="str"/>
-      <x:c r="H1" s="4" t="str"/>
-      <x:c r="I1" s="4" t="str"/>
-      <x:c r="J1" s="4" t="str"/>
-      <x:c r="K1" s="4" t="str"/>
-      <x:c r="L1" s="4" t="str"/>
-      <x:c r="M1" s="4" t="str"/>
-      <x:c r="N1" s="4" t="str"/>
-      <x:c r="O1" s="4" t="str"/>
+    <x:row r="1">
+      <x:c r="A1" s="6" t="str">
+        <x:v>nama_tryout</x:v>
+      </x:c>
+      <x:c r="B1" s="6" t="str">
+        <x:v>kode_soal</x:v>
+      </x:c>
+      <x:c r="C1" s="6" t="str">
+        <x:v>jenis_soal</x:v>
+      </x:c>
+      <x:c r="D1" s="6" t="str">
+        <x:v>sistem_penilaian</x:v>
+      </x:c>
+      <x:c r="E1" s="6" t="str">
+        <x:v>bobot</x:v>
+      </x:c>
+      <x:c r="F1" s="6" t="str">
+        <x:v>topik</x:v>
+      </x:c>
+      <x:c r="G1" s="6" t="str">
+        <x:v>kode_kisi_kisi</x:v>
+      </x:c>
+      <x:c r="H1" s="6" t="str">
+        <x:v>tingkat_kesulitan</x:v>
+      </x:c>
+      <x:c r="I1" s="6" t="str">
+        <x:v>status</x:v>
+      </x:c>
+      <x:c r="J1" s="6" t="str">
+        <x:v>urutan_stimulus</x:v>
+      </x:c>
+      <x:c r="K1" s="6" t="str">
+        <x:v>stimulus_html</x:v>
+      </x:c>
+      <x:c r="L1" s="6" t="str">
+        <x:v>pertanyaan_html</x:v>
+      </x:c>
+      <x:c r="M1" s="6" t="str">
+        <x:v>opsi_a</x:v>
+      </x:c>
+      <x:c r="N1" s="6" t="str">
+        <x:v>opsi_b</x:v>
+      </x:c>
+      <x:c r="O1" s="6" t="str">
+        <x:v>opsi_c</x:v>
+      </x:c>
+      <x:c r="P1" s="6" t="str">
+        <x:v>opsi_d</x:v>
+      </x:c>
+      <x:c r="Q1" s="6" t="str">
+        <x:v>opsi_e</x:v>
+      </x:c>
+      <x:c r="R1" s="6" t="str">
+        <x:v>kunci_jawaban</x:v>
+      </x:c>
+      <x:c r="S1" s="6" t="str">
+        <x:v>pembahasan_html</x:v>
+      </x:c>
+      <x:c r="T1" s="6" t="str">
+        <x:v>catatan_format</x:v>
+      </x:c>
     </x:row>
     <x:row r="2">
-      <x:c r="A2" s="10" t="str">
-        <x:v>tryoutTitle</x:v>
-      </x:c>
-      <x:c r="B2" s="10" t="str">
-        <x:v>questionCode</x:v>
-      </x:c>
-      <x:c r="C2" s="10" t="str">
-        <x:v>topicSlug</x:v>
-      </x:c>
-      <x:c r="D2" s="10" t="str">
-        <x:v>blueprintCode</x:v>
-      </x:c>
-      <x:c r="E2" s="10" t="str">
-        <x:v>difficulty</x:v>
-      </x:c>
-      <x:c r="F2" s="10" t="str">
-        <x:v>status</x:v>
-      </x:c>
-      <x:c r="G2" s="10" t="str">
-        <x:v>stimulusOrder</x:v>
-      </x:c>
-      <x:c r="H2" s="10" t="str">
-        <x:v>questionHtml</x:v>
-      </x:c>
-      <x:c r="I2" s="10" t="str">
-        <x:v>optionA</x:v>
-      </x:c>
-      <x:c r="J2" s="10" t="str">
-        <x:v>optionB</x:v>
-      </x:c>
-      <x:c r="K2" s="10" t="str">
-        <x:v>optionC</x:v>
-      </x:c>
-      <x:c r="L2" s="10" t="str">
-        <x:v>optionD</x:v>
-      </x:c>
-      <x:c r="M2" s="10" t="str">
-        <x:v>optionE</x:v>
-      </x:c>
-      <x:c r="N2" s="10" t="str">
-        <x:v>correctOption</x:v>
-      </x:c>
-      <x:c r="O2" s="10" t="str">
-        <x:v>explanationHtml</x:v>
+      <x:c r="A2" s="12" t="str">
+        <x:v>Tryout Demo IPA SMP</x:v>
+      </x:c>
+      <x:c r="B2" s="12" t="str">
+        <x:v>Q-TKA-PG-001</x:v>
+      </x:c>
+      <x:c r="C2" s="12" t="str">
+        <x:v>SINGLE_CHOICE</x:v>
+      </x:c>
+      <x:c r="D2" s="12" t="str">
+        <x:v>EXACT_MATCH</x:v>
+      </x:c>
+      <x:c r="E2" s="12" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F2" s="12" t="str">
+        <x:v>Gaya dan Gerak</x:v>
+      </x:c>
+      <x:c r="G2" s="12" t="str">
+        <x:v>IPA-SMP-GERAK-001</x:v>
+      </x:c>
+      <x:c r="H2" s="12" t="str">
+        <x:v>Mudah</x:v>
+      </x:c>
+      <x:c r="I2" s="12" t="str">
+        <x:v>PUBLISHED</x:v>
+      </x:c>
+      <x:c r="J2" s="12" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K2" s="12" t="str"/>
+      <x:c r="L2" s="12" t="str">
+        <x:v>&lt;p&gt;Sebuah sepeda bermassa 20 kg mengalami percepatan 2 m/s². Besar gaya yang bekerja pada sepeda adalah ...&lt;/p&gt;</x:v>
+      </x:c>
+      <x:c r="M2" s="12" t="str">
+        <x:v>10 N</x:v>
+      </x:c>
+      <x:c r="N2" s="12" t="str">
+        <x:v>20 N</x:v>
+      </x:c>
+      <x:c r="O2" s="12" t="str">
+        <x:v>40 N</x:v>
+      </x:c>
+      <x:c r="P2" s="12" t="str">
+        <x:v>80 N</x:v>
+      </x:c>
+      <x:c r="Q2" s="12" t="str"/>
+      <x:c r="R2" s="12" t="str">
+        <x:v>C</x:v>
+      </x:c>
+      <x:c r="S2" s="12" t="str">
+        <x:v>&lt;p&gt;F = m × a = 20 × 2 = 40 N.&lt;/p&gt;</x:v>
+      </x:c>
+      <x:c r="T2" s="12" t="str">
+        <x:v>PG biasa: isi satu kunci huruf, misalnya C</x:v>
       </x:c>
     </x:row>
     <x:row r="3">
       <x:c r="A3" s="12" t="str">
-        <x:v>Tryout 1</x:v>
+        <x:v>Tryout Demo IPA SMP</x:v>
       </x:c>
       <x:c r="B3" s="12" t="str">
-        <x:v>Q-IPA-001</x:v>
+        <x:v>Q-TKA-KOM-001</x:v>
       </x:c>
       <x:c r="C3" s="12" t="str">
-        <x:v>sistem-pencernaan-manusia</x:v>
+        <x:v>MULTIPLE_CHOICE</x:v>
       </x:c>
       <x:c r="D3" s="12" t="str">
-        <x:v>KISI-TO1-001</x:v>
-      </x:c>
-      <x:c r="E3" s="12" t="str">
+        <x:v>PARTIAL_NO_PENALTY</x:v>
+      </x:c>
+      <x:c r="E3" s="12" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F3" s="12" t="str">
+        <x:v>Kalor dan Perubahan Wujud</x:v>
+      </x:c>
+      <x:c r="G3" s="12" t="str"/>
+      <x:c r="H3" s="12" t="str">
         <x:v>Sedang</x:v>
       </x:c>
-      <x:c r="F3" s="12" t="str">
+      <x:c r="I3" s="12" t="str">
         <x:v>PUBLISHED</x:v>
       </x:c>
-      <x:c r="G3" s="12" t="n">
+      <x:c r="J3" s="12" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="H3" s="12" t="str">
-        <x:v>&lt;p&gt;Organ yang berfungsi mencerna makanan secara mekanik adalah ...&lt;/p&gt;</x:v>
-      </x:c>
-      <x:c r="I3" s="12" t="str">
-        <x:v>Mulut</x:v>
-      </x:c>
-      <x:c r="J3" s="12" t="str">
-        <x:v>Lambung</x:v>
-      </x:c>
-      <x:c r="K3" s="12" t="str">
-        <x:v>Usus halus</x:v>
-      </x:c>
+      <x:c r="K3" s="12" t="str"/>
       <x:c r="L3" s="12" t="str">
-        <x:v>Hati</x:v>
-      </x:c>
-      <x:c r="M3" s="12" t="str"/>
+        <x:v>&lt;p&gt;Pilih semua pernyataan yang benar tentang energi pada benda yang jatuh.&lt;/p&gt;</x:v>
+      </x:c>
+      <x:c r="M3" s="12" t="str">
+        <x:v>Energi potensial bergantung pada massa, gravitasi, dan ketinggian.</x:v>
+      </x:c>
       <x:c r="N3" s="12" t="str">
-        <x:v>A</x:v>
+        <x:v>Energi kinetik selalu nol selama benda bergerak jatuh.</x:v>
       </x:c>
       <x:c r="O3" s="12" t="str">
-        <x:v>&lt;p&gt;Mulut melakukan pencernaan mekanik melalui gigi. Pembahasan dapat dibaca dengan teks gerak dan suara.&lt;/p&gt;</x:v>
+        <x:v>Energi kinetik bertambah saat kecepatan benda meningkat.</x:v>
+      </x:c>
+      <x:c r="P3" s="12" t="str">
+        <x:v>Energi mekanik tetap jika hambatan udara diabaikan.</x:v>
+      </x:c>
+      <x:c r="Q3" s="12" t="str"/>
+      <x:c r="R3" s="12" t="str">
+        <x:v>A,C,D</x:v>
+      </x:c>
+      <x:c r="S3" s="12" t="str">
+        <x:v>&lt;p&gt;Kunci benar A, C, dan D. Pernyataan B salah karena benda yang bergerak memiliki energi kinetik.&lt;/p&gt;</x:v>
+      </x:c>
+      <x:c r="T3" s="12" t="str">
+        <x:v>PG kompleks: isi beberapa huruf dipisah koma, misalnya A,C,D</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4">
+      <x:c r="A4" s="12" t="str">
+        <x:v>Tryout Demo IPA SMP</x:v>
+      </x:c>
+      <x:c r="B4" s="12" t="str">
+        <x:v>Q-TKA-BS-001</x:v>
+      </x:c>
+      <x:c r="C4" s="12" t="str">
+        <x:v>TRUE_FALSE</x:v>
+      </x:c>
+      <x:c r="D4" s="12" t="str">
+        <x:v>PARTIAL_NO_PENALTY</x:v>
+      </x:c>
+      <x:c r="E4" s="12" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F4" s="12" t="str">
+        <x:v>Ekosistem</x:v>
+      </x:c>
+      <x:c r="G4" s="12" t="str"/>
+      <x:c r="H4" s="12" t="str">
+        <x:v>Sedang</x:v>
+      </x:c>
+      <x:c r="I4" s="12" t="str">
+        <x:v>PUBLISHED</x:v>
+      </x:c>
+      <x:c r="J4" s="12" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K4" s="12" t="str"/>
+      <x:c r="L4" s="12" t="str">
+        <x:v>&lt;p&gt;Tentukan benar atau salah untuk setiap pernyataan tentang susunan atom oksigen.&lt;/p&gt;</x:v>
+      </x:c>
+      <x:c r="M4" s="12" t="str">
+        <x:v>Atom oksigen netral memiliki 8 elektron.</x:v>
+      </x:c>
+      <x:c r="N4" s="12" t="str">
+        <x:v>Jika nomor massanya 16, atom oksigen memiliki 7 neutron.</x:v>
+      </x:c>
+      <x:c r="O4" s="12" t="str">
+        <x:v>Kulit L pada atom oksigen berisi 6 elektron.</x:v>
+      </x:c>
+      <x:c r="P4" s="12" t="str"/>
+      <x:c r="Q4" s="12" t="str"/>
+      <x:c r="R4" s="12" t="str">
+        <x:v>B,S,B</x:v>
+      </x:c>
+      <x:c r="S4" s="12" t="str">
+        <x:v>&lt;p&gt;Oksigen netral memiliki 8 elektron. Nomor massa 16 berarti neutron 8. Kulit L berisi 6 elektron.&lt;/p&gt;</x:v>
+      </x:c>
+      <x:c r="T4" s="12" t="str">
+        <x:v>Benar salah: opsi_a sampai opsi_e diisi pernyataan. Kunci ditulis B,S,B sesuai urutan pernyataan.</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
-  <x:mergeCells>
-    <x:mergeCell ref="A1:O1"/>
-  </x:mergeCells>
+  <x:dataValidations count="3">
+    <x:dataValidation type="list" sqref="C2:C200">
+      <x:formula1>"SINGLE_CHOICE,MULTIPLE_CHOICE,TRUE_FALSE"</x:formula1>
+    </x:dataValidation>
+    <x:dataValidation type="list" sqref="D2:D200">
+      <x:formula1>"EXACT_MATCH,PARTIAL_NO_PENALTY"</x:formula1>
+    </x:dataValidation>
+    <x:dataValidation type="list" sqref="I2:I200">
+      <x:formula1>"DRAFT,REVIEW,PUBLISHED,ARCHIVED"</x:formula1>
+    </x:dataValidation>
+  </x:dataValidations>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="34" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="90" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1">
+      <x:c r="A1" s="5" t="str">
+        <x:v>Kolom</x:v>
+      </x:c>
+      <x:c r="B1" s="5" t="str">
+        <x:v>Keterangan</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2">
+      <x:c r="A2" s="12" t="str">
+        <x:v>jenis_soal</x:v>
+      </x:c>
+      <x:c r="B2" s="12" t="str">
+        <x:v>SINGLE_CHOICE untuk pilihan ganda biasa, MULTIPLE_CHOICE untuk pilihan ganda kompleks, TRUE_FALSE untuk benar atau salah.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3">
+      <x:c r="A3" s="12" t="str">
+        <x:v>sistem_penilaian</x:v>
+      </x:c>
+      <x:c r="B3" s="12" t="str">
+        <x:v>EXACT_MATCH memberi skor penuh hanya jika jawaban sama persis. PARTIAL_NO_PENALTY memberi skor parsial tanpa pengurangan untuk pilihan salah.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4">
+      <x:c r="A4" s="12" t="str">
+        <x:v>kunci_jawaban untuk SINGLE_CHOICE</x:v>
+      </x:c>
+      <x:c r="B4" s="12" t="str">
+        <x:v>Isi satu huruf, contoh C.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5">
+      <x:c r="A5" s="12" t="str">
+        <x:v>kunci_jawaban untuk MULTIPLE_CHOICE</x:v>
+      </x:c>
+      <x:c r="B5" s="12" t="str">
+        <x:v>Isi beberapa huruf dipisah koma, contoh A,C,D.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6">
+      <x:c r="A6" s="12" t="str">
+        <x:v>kunci_jawaban untuk TRUE_FALSE</x:v>
+      </x:c>
+      <x:c r="B6" s="12" t="str">
+        <x:v>Isi B atau S sesuai urutan pernyataan pada opsi_a sampai opsi_e. Contoh B,S,B berarti pernyataan 1 benar, 2 salah, 3 benar.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7">
+      <x:c r="A7" s="12" t="str">
+        <x:v>bobot</x:v>
+      </x:c>
+      <x:c r="B7" s="12" t="str">
+        <x:v>Nilai maksimal per soal. Umumnya 1.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8">
+      <x:c r="A8" s="12" t="str">
+        <x:v>HTML dan LaTeX</x:v>
+      </x:c>
+      <x:c r="B8" s="12" t="str">
+        <x:v>Kolom stimulus_html, pertanyaan_html, opsi, dan pembahasan_html dapat diisi HTML sederhana atau rumus LaTeX.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9">
+      <x:c r="A9" s="12"/>
+      <x:c r="B9" s="12"/>
+    </x:row>
+    <x:row r="10">
+      <x:c r="A10" s="12"/>
+      <x:c r="B10" s="12"/>
+    </x:row>
+    <x:row r="11">
+      <x:c r="A11" s="12"/>
+      <x:c r="B11" s="12"/>
+    </x:row>
+    <x:row r="12">
+      <x:c r="A12" s="12"/>
+      <x:c r="B12" s="12"/>
+    </x:row>
+    <x:row r="13">
+      <x:c r="A13" s="12"/>
+      <x:c r="B13" s="12"/>
+    </x:row>
+    <x:row r="14">
+      <x:c r="A14" s="12"/>
+      <x:c r="B14" s="12"/>
+    </x:row>
+    <x:row r="15">
+      <x:c r="A15" s="12"/>
+      <x:c r="B15" s="12"/>
+    </x:row>
+    <x:row r="16">
+      <x:c r="A16" s="12"/>
+      <x:c r="B16" s="12"/>
+    </x:row>
+    <x:row r="17">
+      <x:c r="A17" s="12"/>
+      <x:c r="B17" s="12"/>
+    </x:row>
+    <x:row r="18">
+      <x:c r="A18" s="12"/>
+      <x:c r="B18" s="12"/>
+    </x:row>
+    <x:row r="19">
+      <x:c r="A19" s="12"/>
+      <x:c r="B19" s="12"/>
+    </x:row>
+    <x:row r="20">
+      <x:c r="A20" s="12"/>
+      <x:c r="B20" s="12"/>
+    </x:row>
+  </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
 </file>